--- a/docs/models.xlsx
+++ b/docs/models.xlsx
@@ -667,7 +667,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>['DS1525+', 'DS1825+', 'DS925+', 'RS2423RP+II', 'RS2825RP+']</t>
+          <t>['RS2423RP+II', 'DS1525+', 'DS1825+', 'DS925+', 'RS2825RP+']</t>
         </is>
       </c>
     </row>

--- a/docs/models.xlsx
+++ b/docs/models.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'7.0': '4.4.180', '7.1': '4.4.180', '7.2': '4.4.302', '7.3': '4.4.302'}</t>
+          <t>{'7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180', '7.0': '7.0-4.4.180'}</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -458,7 +458,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'7.0': '4.4.180', '7.1': '4.4.180', '7.2': '4.4.302', '7.3': '4.4.302'}</t>
+          <t>{'7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180', '7.0': '7.0-4.4.180'}</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -475,7 +475,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'7.0': '4.4.180', '7.1': '4.4.180', '7.2': '4.4.302', '7.3': '4.4.302'}</t>
+          <t>{'7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180', '7.0': '7.0-4.4.180'}</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -492,7 +492,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'7.0': '4.4.180', '7.1': '4.4.180', '7.2': '4.4.302', '7.3': '4.4.302'}</t>
+          <t>{'7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180'}</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -509,7 +509,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'7.0': '4.4.180', '7.1': '4.4.180', '7.2': '4.4.302', '7.3': '4.4.302'}</t>
+          <t>{'7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180'}</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -526,7 +526,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'7.0': '4.4.180', '7.1': '4.4.180', '7.2': '4.4.302', '7.3': '4.4.302'}</t>
+          <t>{'7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180', '7.0': '7.0-4.4.180'}</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'7.0': '4.4.180', '7.1': '4.4.180', '7.2': '4.4.302', '7.3': '4.4.302'}</t>
+          <t>{'7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180', '7.0': '7.0-4.4.180'}</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -560,7 +560,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'7.0': '4.4.180', '7.1': '4.4.180', '7.2': '4.4.302', '7.3': '4.4.302'}</t>
+          <t>{'7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180', '7.0': '7.0-4.4.180'}</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'7.0': '4.4.180', '7.1': '4.4.180', '7.2': '4.4.302', '7.3': '4.4.302'}</t>
+          <t>{'7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180'}</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'7.0': '4.4.180', '7.1': '4.4.180', '7.2': '4.4.302', '7.3': '4.4.302'}</t>
+          <t>{'7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180', '7.0': '7.0-4.4.180'}</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'7.1': '7.1-5.10.55', '7.2': '7.2-5.10.55', '7.3': '7.3-5.10.55'}</t>
+          <t>{'7.3': '7.3-5.10.55', '7.2': '7.2-5.10.55', '7.1': '7.1-5.10.55'}</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'7.1': '7.1-5.10.55', '7.2': '7.2-5.10.55', '7.3': '7.3-5.10.55'}</t>
+          <t>{'7.3': '7.3-5.10.55', '7.2': '7.2-5.10.55'}</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'7.1': '7.1-5.10.55', '7.2': '7.2-5.10.55', '7.3': '7.3-5.10.55'}</t>
+          <t>{'7.3': '7.3-5.10.55', '7.2': '7.2-5.10.55'}</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'7.1': '7.1-5.10.55', '7.2': '7.2-5.10.55', '7.3': '7.3-5.10.55'}</t>
+          <t>{'7.3': '7.3-5.10.55', '7.2': '7.2-5.10.55'}</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">

--- a/docs/models.xlsx
+++ b/docs/models.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180', '7.0': '7.0-4.4.180'}</t>
+          <t>{'7.4': '7.4-4.4.302', '7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180', '7.0': '7.0-4.4.180'}</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -458,7 +458,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180', '7.0': '7.0-4.4.180'}</t>
+          <t>{'7.4': '7.4-4.4.302', '7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180', '7.0': '7.0-4.4.180'}</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -475,7 +475,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180', '7.0': '7.0-4.4.180'}</t>
+          <t>{'7.4': '7.4-4.4.302', '7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180', '7.0': '7.0-4.4.180'}</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -492,7 +492,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180'}</t>
+          <t>{'7.4': '7.4-4.4.302', '7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180'}</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -509,7 +509,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180'}</t>
+          <t>{'7.4': '7.4-4.4.302', '7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180'}</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -526,7 +526,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180', '7.0': '7.0-4.4.180'}</t>
+          <t>{'7.4': '7.4-4.4.302', '7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180', '7.0': '7.0-4.4.180'}</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180', '7.0': '7.0-4.4.180'}</t>
+          <t>{'7.4': '7.4-4.4.302', '7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180', '7.0': '7.0-4.4.180'}</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -555,119 +555,153 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>purley</t>
+          <t>icelaked</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180', '7.0': '7.0-4.4.180'}</t>
+          <t>{'7.4': '7.4-5.10.55'}</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>['FS6400', 'HD6500']</t>
+          <t>['FS3420', 'RS1626xs+', 'RS3626xs', 'RS4826xs+', 'RS6426xs+']</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>r1000</t>
+          <t>purley</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180'}</t>
+          <t>{'7.4': '7.4-4.4.302', '7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180', '7.0': '7.0-4.4.180'}</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>['DS1522+', 'DS723+', 'DS923+', 'RS422+']</t>
+          <t>['FS6400', 'HD6500']</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>v1000</t>
+          <t>r1000</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180', '7.0': '7.0-4.4.180'}</t>
+          <t>{'7.4': '7.4-4.4.302', '7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180'}</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>['DS1621+', 'DS1821+', 'DS1823xs+', 'DS2422+', 'FS2500', 'RS1221+', 'RS1221RP+', 'RS2421+', 'RS2421RP+', 'RS2423+', 'RS2423RP+', 'RS2821RP+', 'RS822+', 'RS822RP+']</t>
+          <t>['DS1522+', 'DS723+', 'DS923+', 'RS422+']</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>epyc7002</t>
+          <t>v1000</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'7.3': '7.3-5.10.55', '7.2': '7.2-5.10.55', '7.1': '7.1-5.10.55'}</t>
+          <t>{'7.4': '7.4-4.4.302', '7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180', '7.0': '7.0-4.4.180'}</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>['SA6400']</t>
+          <t>['DS1621+', 'DS1821+', 'DS1823xs+', 'DS2422+', 'FS2500', 'RS1221+', 'RS1221RP+', 'RS2421+', 'RS2421RP+', 'RS2423+', 'RS2423RP+', 'RS2821RP+', 'RS822+', 'RS822RP+']</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>geminilakenk</t>
+          <t>epyc7002</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'7.3': '7.3-5.10.55', '7.2': '7.2-5.10.55'}</t>
+          <t>{'7.4': '7.4-5.10.55', '7.3': '7.3-5.10.55', '7.2': '7.2-5.10.55', '7.1': '7.1-5.10.55'}</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>['DS225+', 'DS425+']</t>
+          <t>['SA6400']</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>r1000nk</t>
+          <t>epyc7003ntb</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'7.3': '7.3-5.10.55', '7.2': '7.2-5.10.55'}</t>
+          <t>{'7.4': '7.4-5.10.55'}</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>['DS725+']</t>
+          <t>['PAS7700']</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>geminilakenk</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>{'7.4': '7.4-5.10.55', '7.3': '7.3-5.10.55', '7.2': '7.2-5.10.55'}</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>['DS225+', 'DS425+', 'FS200T']</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>r1000nk</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>{'7.4': '7.4-5.10.55', '7.3': '7.3-5.10.55', '7.2': '7.2-5.10.55'}</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>['DS725+']</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>v1000nk</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>{'7.3': '7.3-5.10.55', '7.2': '7.2-5.10.55'}</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>['RS2423RP+II', 'DS1525+', 'DS1825+', 'DS925+', 'RS2825RP+']</t>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>{'7.4': '7.4-5.10.55', '7.3': '7.3-5.10.55', '7.2': '7.2-5.10.55'}</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>['RS2423RP+II', 'DS1525+', 'DS1825+', 'DS925+', 'RS2825RP+', 'RS826+', 'RS826RP+']</t>
         </is>
       </c>
     </row>

--- a/docs/models.xlsx
+++ b/docs/models.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -555,85 +555,85 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>icelaked</t>
+          <t>purley</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'7.4': '7.4-5.10.55'}</t>
+          <t>{'7.4': '7.4-4.4.302', '7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180', '7.0': '7.0-4.4.180'}</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>['FS3420', 'RS1626xs+', 'RS3626xs', 'RS4826xs+', 'RS6426xs+']</t>
+          <t>['FS6400', 'HD6500']</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>purley</t>
+          <t>r1000</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'7.4': '7.4-4.4.302', '7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180', '7.0': '7.0-4.4.180'}</t>
+          <t>{'7.4': '7.4-4.4.302', '7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180'}</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>['FS6400', 'HD6500']</t>
+          <t>['DS1522+', 'DS723+', 'DS923+', 'RS422+']</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>r1000</t>
+          <t>v1000</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'7.4': '7.4-4.4.302', '7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180'}</t>
+          <t>{'7.4': '7.4-4.4.302', '7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180', '7.0': '7.0-4.4.180'}</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>['DS1522+', 'DS723+', 'DS923+', 'RS422+']</t>
+          <t>['DS1621+', 'DS1821+', 'DS1823xs+', 'DS2422+', 'FS2500', 'RS1221+', 'RS1221RP+', 'RS2421+', 'RS2421RP+', 'RS2423+', 'RS2423RP+', 'RS2821RP+', 'RS822+', 'RS822RP+']</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>v1000</t>
+          <t>epyc7002</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'7.4': '7.4-4.4.302', '7.3': '7.3-4.4.302', '7.2': '7.2-4.4.302', '7.1': '7.1-4.4.180', '7.0': '7.0-4.4.180'}</t>
+          <t>{'7.4': '7.4-5.10.55', '7.3': '7.3-5.10.55', '7.2': '7.2-5.10.55', '7.1': '7.1-5.10.55'}</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>['DS1621+', 'DS1821+', 'DS1823xs+', 'DS2422+', 'FS2500', 'RS1221+', 'RS1221RP+', 'RS2421+', 'RS2421RP+', 'RS2423+', 'RS2423RP+', 'RS2821RP+', 'RS822+', 'RS822RP+']</t>
+          <t>['SA6400']</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>epyc7002</t>
+          <t>epyc7003</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'7.4': '7.4-5.10.55', '7.3': '7.3-5.10.55', '7.2': '7.2-5.10.55', '7.1': '7.1-5.10.55'}</t>
+          <t>{'7.4': '7.4-5.10.55'}</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>['SA6400']</t>
+          <t>['FS6420']</t>
         </is>
       </c>
     </row>
@@ -674,32 +674,49 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>r1000nk</t>
+          <t>icelaked</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'7.4': '7.4-5.10.55', '7.3': '7.3-5.10.55', '7.2': '7.2-5.10.55'}</t>
+          <t>{'7.4': '7.4-5.10.55'}</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>['DS725+']</t>
+          <t>['FS3420', 'RS1626xs+', 'RS3626xs', 'RS4826xs+', 'RS6426xs+']</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>r1000nk</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>{'7.4': '7.4-5.10.55', '7.3': '7.3-5.10.55', '7.2': '7.2-5.10.55'}</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>['DS725+']</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>v1000nk</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>{'7.4': '7.4-5.10.55', '7.3': '7.3-5.10.55', '7.2': '7.2-5.10.55'}</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>['RS2423RP+II', 'DS1525+', 'DS1825+', 'DS925+', 'RS2825RP+', 'RS826+', 'RS826RP+']</t>
         </is>

--- a/docs/models.xlsx
+++ b/docs/models.xlsx
@@ -667,7 +667,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>['DS225+', 'DS425+', 'FS200T']</t>
+          <t>['FS200T', 'DS225+', 'DS425+']</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>['DS725+']</t>
+          <t>['DS725neo+', 'DS725+']</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>['RS2423RP+II', 'DS1525+', 'DS1825+', 'DS925+', 'RS2825RP+', 'RS826+', 'RS826RP+']</t>
+          <t>['DS1525neo+', 'DS1825neo+', 'DVA7400', 'RS1226+', 'RS1226RP+', 'RS2423RP+II', 'RS826+', 'RS826RP+', 'DS1525+', 'DS1825+', 'DS925+', 'RS2825RP+']</t>
         </is>
       </c>
     </row>

--- a/docs/models.xlsx
+++ b/docs/models.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>['FS6420']</t>
+          <t>['FS6420', 'RS11626xs+']</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>['FS200T', 'DS225+', 'DS425+']</t>
+          <t>['DS225+', 'DS425+', 'FS200T']</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>['DS725neo+', 'DS725+']</t>
+          <t>['DS725+', 'DS725neo+']</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>['DS1525neo+', 'DS1825neo+', 'DVA7400', 'RS1226+', 'RS1226RP+', 'RS2423RP+II', 'RS826+', 'RS826RP+', 'DS1525+', 'DS1825+', 'DS925+', 'RS2825RP+']</t>
+          <t>['DS1525+', 'DS1525neo+', 'DS1825+', 'DS1825neo+', 'DS925+', 'DVA7400', 'RS1226+', 'RS1226RP+', 'RS2423RP+II', 'RS2825RP+', 'RS826+', 'RS826RP+']</t>
         </is>
       </c>
     </row>

--- a/docs/models.xlsx
+++ b/docs/models.xlsx
@@ -718,7 +718,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>['DS1525+', 'DS1525neo+', 'DS1825+', 'DS1825neo+', 'DS925+', 'DVA7400', 'RS1226+', 'RS1226RP+', 'RS2423RP+II', 'RS2825RP+', 'RS826+', 'RS826RP+']</t>
+          <t>['DS1525+', 'DS1525neo+', 'DS1825+', 'DS1825neo+', 'DS925+', 'DS925neo+', 'DVA7400', 'RS1226+', 'RS1226RP+', 'RS2423RP+II', 'RS2825RP+', 'RS826+', 'RS826RP+']</t>
         </is>
       </c>
     </row>
